--- a/results/mvp_primary_db.xlsx
+++ b/results/mvp_primary_db.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Nicco SSD/FOMO DATA/outputs/split_workbooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/niccolocaselli/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD943A8-BF3D-C14C-99C5-211AD7E7C3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA3C819-11E5-C74C-B66D-5D362527AAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="V-JEPA" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="149">
   <si>
     <t>ViT-L/16 - primary metric: Pair Consistency</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>MLP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Attentive</t>
@@ -594,6 +591,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -609,10 +610,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -937,34 +934,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
     </row>
     <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1407,29 +1404,29 @@
         <v>24</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="5">
-        <v>100</v>
+        <v>95.193929173692993</v>
       </c>
       <c r="T8" s="5">
-        <v>94.893832153690596</v>
+        <v>77.755308392315399</v>
       </c>
       <c r="U8" s="5">
-        <v>93.023255813953398</v>
+        <v>77.249747219413507</v>
       </c>
       <c r="V8" s="5">
-        <v>100</v>
+        <v>90.3878583473861</v>
       </c>
       <c r="W8" s="5">
-        <v>90.798786653185005</v>
+        <v>59.8584428715874</v>
       </c>
       <c r="X8" s="5">
-        <v>86.855409504549996</v>
+        <v>59.453993933265899</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1473,29 +1470,29 @@
         <v>24</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R9" s="2"/>
       <c r="S9" s="5">
-        <v>95.193929173692993</v>
+        <v>99.224283305227601</v>
       </c>
       <c r="T9" s="5">
-        <v>77.755308392315399</v>
+        <v>85.338725985844206</v>
       </c>
       <c r="U9" s="5">
-        <v>77.249747219413507</v>
+        <v>83.720930232558104</v>
       </c>
       <c r="V9" s="5">
-        <v>90.3878583473861</v>
+        <v>98.448566610455302</v>
       </c>
       <c r="W9" s="5">
-        <v>59.8584428715874</v>
+        <v>72.800808897876607</v>
       </c>
       <c r="X9" s="5">
-        <v>59.453993933265899</v>
+        <v>70.171890798786606</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1539,29 +1536,29 @@
         <v>24</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R10" s="2"/>
       <c r="S10" s="5">
-        <v>99.224283305227601</v>
+        <v>100</v>
       </c>
       <c r="T10" s="5">
-        <v>85.338725985844206</v>
+        <v>94.893832153690596</v>
       </c>
       <c r="U10" s="5">
-        <v>83.720930232558104</v>
+        <v>93.023255813953398</v>
       </c>
       <c r="V10" s="5">
-        <v>98.448566610455302</v>
+        <v>100</v>
       </c>
       <c r="W10" s="5">
-        <v>72.800808897876607</v>
+        <v>90.798786653185005</v>
       </c>
       <c r="X10" s="5">
-        <v>70.171890798786606</v>
+        <v>86.855409504549996</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1569,7 +1566,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>15</v>
@@ -1602,7 +1599,7 @@
         <v>16</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>17</v>
@@ -1635,7 +1632,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>18</v>
@@ -1668,7 +1665,7 @@
         <v>16</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>19</v>
@@ -1701,7 +1698,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>20</v>
@@ -1734,7 +1731,7 @@
         <v>16</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>21</v>
@@ -1767,7 +1764,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>22</v>
@@ -1800,7 +1797,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>23</v>
@@ -1861,34 +1858,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
+      <c r="N1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
     </row>
     <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2493,7 +2490,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>15</v>
@@ -2526,7 +2523,7 @@
         <v>16</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>17</v>
@@ -2559,7 +2556,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>18</v>
@@ -2592,7 +2589,7 @@
         <v>16</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>19</v>
@@ -2625,7 +2622,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>20</v>
@@ -2658,7 +2655,7 @@
         <v>16</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>21</v>
@@ -2691,7 +2688,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>22</v>
@@ -2724,7 +2721,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>23</v>
@@ -2801,64 +2798,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
-      <c r="AA1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-      <c r="AH1" s="12"/>
-      <c r="AI1" s="12"/>
-      <c r="AJ1" s="12"/>
-      <c r="AK1" s="12"/>
+      <c r="AA1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14"/>
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
-      <c r="AN1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="AO1" s="12"/>
-      <c r="AP1" s="12"/>
-      <c r="AQ1" s="12"/>
-      <c r="AR1" s="12"/>
-      <c r="AS1" s="12"/>
-      <c r="AT1" s="12"/>
-      <c r="AU1" s="12"/>
-      <c r="AV1" s="12"/>
-      <c r="AW1" s="12"/>
-      <c r="AX1" s="12"/>
+      <c r="AN1" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14"/>
+      <c r="AQ1" s="14"/>
+      <c r="AR1" s="14"/>
+      <c r="AS1" s="14"/>
+      <c r="AT1" s="14"/>
+      <c r="AU1" s="14"/>
+      <c r="AV1" s="14"/>
+      <c r="AW1" s="14"/>
+      <c r="AX1" s="14"/>
     </row>
     <row r="2" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3002,16 +2999,16 @@
     </row>
     <row r="3" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="5">
@@ -3068,16 +3065,16 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
       <c r="AA3" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AE3" s="2"/>
       <c r="AF3" s="5">
@@ -3134,7 +3131,7 @@
     </row>
     <row r="4" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
@@ -3200,16 +3197,16 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE4" s="2"/>
       <c r="AF4" s="5">
@@ -3266,16 +3263,16 @@
     </row>
     <row r="5" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="5">
@@ -3332,16 +3329,16 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AE5" s="2"/>
       <c r="AF5" s="5">
@@ -3398,7 +3395,7 @@
     </row>
     <row r="6" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
@@ -3464,16 +3461,16 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE6" s="2"/>
       <c r="AF6" s="5">
@@ -3530,16 +3527,16 @@
     </row>
     <row r="7" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="5">
@@ -3596,16 +3593,16 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AE7" s="2"/>
       <c r="AF7" s="5">
@@ -3662,7 +3659,7 @@
     </row>
     <row r="8" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
@@ -3728,16 +3725,16 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE8" s="2"/>
       <c r="AF8" s="5">
@@ -3794,16 +3791,16 @@
     </row>
     <row r="9" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="5">
@@ -3860,16 +3857,16 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AE9" s="2"/>
       <c r="AF9" s="5">
@@ -3926,7 +3923,7 @@
     </row>
     <row r="10" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>24</v>
@@ -3992,16 +3989,16 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE10" s="2"/>
       <c r="AF10" s="5">
@@ -4058,16 +4055,16 @@
     </row>
     <row r="11" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="5">
@@ -4094,7 +4091,7 @@
         <v>13</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>15</v>
@@ -4124,16 +4121,16 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AE11" s="2"/>
       <c r="AF11" s="5">
@@ -4160,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="AO11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP11" s="2" t="s">
         <v>17</v>
@@ -4190,10 +4187,10 @@
     </row>
     <row r="12" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>15</v>
@@ -4226,7 +4223,7 @@
         <v>13</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>18</v>
@@ -4256,16 +4253,16 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE12" s="2"/>
       <c r="AF12" s="5">
@@ -4292,7 +4289,7 @@
         <v>16</v>
       </c>
       <c r="AO12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP12" s="2" t="s">
         <v>19</v>
@@ -4322,16 +4319,16 @@
     </row>
     <row r="13" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="5">
@@ -4358,7 +4355,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>20</v>
@@ -4388,16 +4385,16 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
       <c r="AA13" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AE13" s="2"/>
       <c r="AF13" s="5">
@@ -4424,7 +4421,7 @@
         <v>16</v>
       </c>
       <c r="AO13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP13" s="2" t="s">
         <v>21</v>
@@ -4454,10 +4451,10 @@
     </row>
     <row r="14" spans="1:50" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>18</v>
@@ -4490,7 +4487,7 @@
         <v>13</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>22</v>
@@ -4520,16 +4517,16 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE14" s="2"/>
       <c r="AF14" s="5">
@@ -4556,7 +4553,7 @@
         <v>16</v>
       </c>
       <c r="AO14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP14" s="2" t="s">
         <v>23</v>
@@ -4618,34 +4615,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
     </row>
     <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -5250,7 +5247,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>15</v>
@@ -5283,7 +5280,7 @@
         <v>16</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>17</v>
@@ -5316,7 +5313,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>18</v>
@@ -5349,7 +5346,7 @@
         <v>16</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>19</v>
@@ -5382,7 +5379,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>20</v>
@@ -5415,7 +5412,7 @@
         <v>16</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>21</v>
@@ -5448,7 +5445,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>22</v>
@@ -5481,7 +5478,7 @@
         <v>16</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>23</v>
@@ -5552,49 +5549,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
-      <c r="AA1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-      <c r="AH1" s="12"/>
-      <c r="AI1" s="12"/>
-      <c r="AJ1" s="12"/>
-      <c r="AK1" s="12"/>
+      <c r="AA1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14"/>
     </row>
     <row r="2" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -5703,16 +5700,16 @@
     </row>
     <row r="3" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="5">
@@ -5802,7 +5799,7 @@
     </row>
     <row r="4" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
@@ -5901,16 +5898,16 @@
     </row>
     <row r="5" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="5">
@@ -6000,7 +5997,7 @@
     </row>
     <row r="6" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
@@ -6099,16 +6096,16 @@
     </row>
     <row r="7" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="5">
@@ -6198,7 +6195,7 @@
     </row>
     <row r="8" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
@@ -6297,16 +6294,16 @@
     </row>
     <row r="9" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="5">
@@ -6396,7 +6393,7 @@
     </row>
     <row r="10" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>24</v>
@@ -6495,16 +6492,16 @@
     </row>
     <row r="11" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="5">
@@ -6531,7 +6528,7 @@
         <v>13</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>15</v>
@@ -6564,7 +6561,7 @@
         <v>16</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC11" s="2" t="s">
         <v>17</v>
@@ -6594,10 +6591,10 @@
     </row>
     <row r="12" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>15</v>
@@ -6630,7 +6627,7 @@
         <v>13</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>18</v>
@@ -6663,7 +6660,7 @@
         <v>16</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC12" s="2" t="s">
         <v>19</v>
@@ -6693,16 +6690,16 @@
     </row>
     <row r="13" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="5">
@@ -6729,7 +6726,7 @@
         <v>13</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>20</v>
@@ -6762,7 +6759,7 @@
         <v>16</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>21</v>
@@ -6792,10 +6789,10 @@
     </row>
     <row r="14" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>18</v>
@@ -6828,7 +6825,7 @@
         <v>13</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>22</v>
@@ -6861,7 +6858,7 @@
         <v>16</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC14" s="2" t="s">
         <v>23</v>
@@ -6924,34 +6921,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
+      <c r="N1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
     </row>
     <row r="2" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -7025,16 +7022,16 @@
     </row>
     <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="D3" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="5">
@@ -7058,7 +7055,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>14</v>
@@ -7067,7 +7064,7 @@
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" s="5">
@@ -7091,16 +7088,16 @@
     </row>
     <row r="4" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>32</v>
+      <c r="C4" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="5">
@@ -7124,7 +7121,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>14</v>
@@ -7133,7 +7130,7 @@
         <v>2</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R4" s="2"/>
       <c r="S4" s="5">
@@ -7157,16 +7154,16 @@
     </row>
     <row r="5" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="5">
@@ -7190,7 +7187,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>14</v>
@@ -7199,7 +7196,7 @@
         <v>3</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R5" s="2"/>
       <c r="S5" s="5">
@@ -7223,16 +7220,16 @@
     </row>
     <row r="6" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="11" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="5">
@@ -7256,7 +7253,7 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>14</v>
@@ -7265,7 +7262,7 @@
         <v>4</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" s="5">
@@ -7289,16 +7286,16 @@
     </row>
     <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="5">
@@ -7322,7 +7319,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>14</v>
@@ -7331,7 +7328,7 @@
         <v>5</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R7" s="2"/>
       <c r="S7" s="5">
@@ -7355,16 +7352,16 @@
     </row>
     <row r="8" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="5">
@@ -7388,7 +7385,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>14</v>
@@ -7397,7 +7394,7 @@
         <v>6</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="5">
@@ -7421,16 +7418,16 @@
     </row>
     <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="5">
@@ -7454,7 +7451,7 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>14</v>
@@ -7463,7 +7460,7 @@
         <v>7</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R9" s="2"/>
       <c r="S9" s="5">
@@ -7487,16 +7484,16 @@
     </row>
     <row r="10" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="5">
@@ -7520,7 +7517,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>14</v>
@@ -7529,7 +7526,7 @@
         <v>8</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R10" s="2"/>
       <c r="S10" s="5">
@@ -7553,16 +7550,16 @@
     </row>
     <row r="11" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="5">
@@ -7586,7 +7583,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>14</v>
@@ -7595,7 +7592,7 @@
         <v>9</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="5">
@@ -7619,16 +7616,16 @@
     </row>
     <row r="12" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="5">
@@ -7652,7 +7649,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>14</v>
@@ -7661,7 +7658,7 @@
         <v>10</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R12" s="2"/>
       <c r="S12" s="5">
@@ -7685,16 +7682,16 @@
     </row>
     <row r="13" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="5">
@@ -7718,7 +7715,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>14</v>
@@ -7727,7 +7724,7 @@
         <v>11</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R13" s="2"/>
       <c r="S13" s="5">
@@ -7751,16 +7748,16 @@
     </row>
     <row r="14" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="5">
@@ -7784,7 +7781,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>14</v>
@@ -7793,7 +7790,7 @@
         <v>12</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R14" s="2"/>
       <c r="S14" s="5">
@@ -7817,16 +7814,16 @@
     </row>
     <row r="15" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>33</v>
+      <c r="C15" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="5">
@@ -7850,7 +7847,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>14</v>
@@ -7859,7 +7856,7 @@
         <v>13</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R15" s="2"/>
       <c r="S15" s="5">
@@ -7883,16 +7880,16 @@
     </row>
     <row r="16" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="5">
@@ -7916,7 +7913,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>14</v>
@@ -7925,7 +7922,7 @@
         <v>14</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R16" s="2"/>
       <c r="S16" s="5">
@@ -7949,16 +7946,16 @@
     </row>
     <row r="17" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="5">
@@ -7982,7 +7979,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>14</v>
@@ -7991,7 +7988,7 @@
         <v>15</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R17" s="2"/>
       <c r="S17" s="5">
@@ -8015,16 +8012,16 @@
     </row>
     <row r="18" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="5">
@@ -8048,7 +8045,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>14</v>
@@ -8057,7 +8054,7 @@
         <v>16</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R18" s="2"/>
       <c r="S18" s="5">
@@ -8081,16 +8078,16 @@
     </row>
     <row r="19" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="5">
@@ -8114,7 +8111,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>14</v>
@@ -8123,7 +8120,7 @@
         <v>17</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R19" s="2"/>
       <c r="S19" s="5">
@@ -8147,16 +8144,16 @@
     </row>
     <row r="20" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="5">
@@ -8180,7 +8177,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>14</v>
@@ -8189,7 +8186,7 @@
         <v>18</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="5">
@@ -8213,16 +8210,16 @@
     </row>
     <row r="21" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="5">
@@ -8246,7 +8243,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>14</v>
@@ -8255,7 +8252,7 @@
         <v>19</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R21" s="2"/>
       <c r="S21" s="5">
@@ -8279,16 +8276,16 @@
     </row>
     <row r="22" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="5">
@@ -8312,7 +8309,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>14</v>
@@ -8321,7 +8318,7 @@
         <v>20</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R22" s="2"/>
       <c r="S22" s="5">
@@ -8345,16 +8342,16 @@
     </row>
     <row r="23" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="5">
@@ -8378,7 +8375,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>14</v>
@@ -8387,7 +8384,7 @@
         <v>21</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R23" s="2"/>
       <c r="S23" s="5">
@@ -8411,16 +8408,16 @@
     </row>
     <row r="24" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="5">
@@ -8444,7 +8441,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>14</v>
@@ -8453,7 +8450,7 @@
         <v>22</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R24" s="2"/>
       <c r="S24" s="5">
@@ -8477,16 +8474,16 @@
     </row>
     <row r="25" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>31</v>
+      <c r="C25" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="5">
@@ -8510,7 +8507,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>14</v>
@@ -8519,7 +8516,7 @@
         <v>23</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R25" s="2"/>
       <c r="S25" s="5">
@@ -8543,16 +8540,16 @@
     </row>
     <row r="26" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>35</v>
+      <c r="C26" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="5">
@@ -8576,7 +8573,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>14</v>
@@ -8585,7 +8582,7 @@
         <v>24</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R26" s="2"/>
       <c r="S26" s="5">
@@ -8609,16 +8606,16 @@
     </row>
     <row r="27" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="5">
@@ -8642,7 +8639,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>14</v>
@@ -8651,7 +8648,7 @@
         <v>25</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R27" s="2"/>
       <c r="S27" s="5">
@@ -8675,16 +8672,16 @@
     </row>
     <row r="28" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="5">
@@ -8708,7 +8705,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>14</v>
@@ -8717,7 +8714,7 @@
         <v>26</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R28" s="2"/>
       <c r="S28" s="5">
@@ -8741,16 +8738,16 @@
     </row>
     <row r="29" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="5">
@@ -8774,7 +8771,7 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>14</v>
@@ -8783,7 +8780,7 @@
         <v>27</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R29" s="2"/>
       <c r="S29" s="5">
@@ -8807,16 +8804,16 @@
     </row>
     <row r="30" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="5">
@@ -8840,7 +8837,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>14</v>
@@ -8849,7 +8846,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" s="5">
@@ -8873,16 +8870,16 @@
     </row>
     <row r="31" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="5">
@@ -8906,7 +8903,7 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>14</v>
@@ -8915,7 +8912,7 @@
         <v>29</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R31" s="2"/>
       <c r="S31" s="5">
@@ -8939,16 +8936,16 @@
     </row>
     <row r="32" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="5">
@@ -8972,7 +8969,7 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>14</v>
@@ -8981,7 +8978,7 @@
         <v>30</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R32" s="2"/>
       <c r="S32" s="5">
@@ -9005,16 +9002,16 @@
     </row>
     <row r="33" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="5">
@@ -9038,7 +9035,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>14</v>
@@ -9047,7 +9044,7 @@
         <v>31</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R33" s="2"/>
       <c r="S33" s="5">
@@ -9071,16 +9068,16 @@
     </row>
     <row r="34" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="5">
@@ -9104,7 +9101,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>14</v>
@@ -9113,7 +9110,7 @@
         <v>32</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R34" s="2"/>
       <c r="S34" s="5">
@@ -9137,16 +9134,16 @@
     </row>
     <row r="35" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="5">
@@ -9170,7 +9167,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>14</v>
@@ -9179,7 +9176,7 @@
         <v>33</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="5">
@@ -9203,16 +9200,16 @@
     </row>
     <row r="36" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="5">
@@ -9236,7 +9233,7 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>14</v>
@@ -9245,7 +9242,7 @@
         <v>34</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R36" s="2"/>
       <c r="S36" s="5">
@@ -9269,16 +9266,16 @@
     </row>
     <row r="37" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>36</v>
+      <c r="C37" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="5">
@@ -9302,7 +9299,7 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>14</v>
@@ -9311,7 +9308,7 @@
         <v>35</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R37" s="2"/>
       <c r="S37" s="5">
@@ -9335,16 +9332,16 @@
     </row>
     <row r="38" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="5">
@@ -9368,7 +9365,7 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>14</v>
@@ -9377,7 +9374,7 @@
         <v>36</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R38" s="2"/>
       <c r="S38" s="5">
@@ -9401,16 +9398,16 @@
     </row>
     <row r="39" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="5">
@@ -9434,7 +9431,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>14</v>
@@ -9443,7 +9440,7 @@
         <v>37</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R39" s="2"/>
       <c r="S39" s="5">
@@ -9467,16 +9464,16 @@
     </row>
     <row r="40" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="5">
@@ -9500,7 +9497,7 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>14</v>
@@ -9509,7 +9506,7 @@
         <v>38</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R40" s="2"/>
       <c r="S40" s="5">
@@ -9533,16 +9530,16 @@
     </row>
     <row r="41" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="5">
@@ -9566,7 +9563,7 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>14</v>
@@ -9575,7 +9572,7 @@
         <v>39</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R41" s="2"/>
       <c r="S41" s="5">
@@ -9599,16 +9596,16 @@
     </row>
     <row r="42" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>34</v>
+      <c r="C42" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="5">
@@ -9632,7 +9629,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>14</v>
@@ -9641,7 +9638,7 @@
         <v>40</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R42" s="2"/>
       <c r="S42" s="5">
@@ -9665,16 +9662,16 @@
     </row>
     <row r="43" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="5">
@@ -9698,7 +9695,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>24</v>
@@ -9707,7 +9704,7 @@
         <v>1</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R43" s="2"/>
       <c r="S43" s="5">
@@ -9731,16 +9728,16 @@
     </row>
     <row r="44" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="5">
@@ -9764,7 +9761,7 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>24</v>
@@ -9773,7 +9770,7 @@
         <v>2</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R44" s="2"/>
       <c r="S44" s="5">
@@ -9797,16 +9794,16 @@
     </row>
     <row r="45" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="5">
@@ -9830,7 +9827,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>24</v>
@@ -9839,7 +9836,7 @@
         <v>3</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R45" s="2"/>
       <c r="S45" s="5">
@@ -9863,16 +9860,16 @@
     </row>
     <row r="46" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="5">
@@ -9896,7 +9893,7 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>24</v>
@@ -9905,7 +9902,7 @@
         <v>4</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R46" s="2"/>
       <c r="S46" s="5">
@@ -9929,16 +9926,16 @@
     </row>
     <row r="47" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="5">
@@ -9962,7 +9959,7 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>24</v>
@@ -9971,7 +9968,7 @@
         <v>5</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R47" s="2"/>
       <c r="S47" s="5">
@@ -9995,16 +9992,16 @@
     </row>
     <row r="48" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="5">
@@ -10028,7 +10025,7 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>24</v>
@@ -10037,7 +10034,7 @@
         <v>6</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R48" s="2"/>
       <c r="S48" s="5">
@@ -10061,16 +10058,16 @@
     </row>
     <row r="49" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="5">
@@ -10094,7 +10091,7 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>24</v>
@@ -10103,7 +10100,7 @@
         <v>7</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R49" s="2"/>
       <c r="S49" s="5">
@@ -10127,16 +10124,16 @@
     </row>
     <row r="50" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C50" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="5">
@@ -10160,7 +10157,7 @@
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>24</v>
@@ -10169,7 +10166,7 @@
         <v>8</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R50" s="2"/>
       <c r="S50" s="5">
@@ -10193,16 +10190,16 @@
     </row>
     <row r="51" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="5">
@@ -10226,7 +10223,7 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>24</v>
@@ -10235,7 +10232,7 @@
         <v>9</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R51" s="2"/>
       <c r="S51" s="5">
@@ -10259,16 +10256,16 @@
     </row>
     <row r="52" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="5">
@@ -10292,7 +10289,7 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>24</v>
@@ -10301,7 +10298,7 @@
         <v>10</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R52" s="2"/>
       <c r="S52" s="5">
@@ -10325,16 +10322,16 @@
     </row>
     <row r="53" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="5">
@@ -10358,7 +10355,7 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>24</v>
@@ -10367,7 +10364,7 @@
         <v>11</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R53" s="2"/>
       <c r="S53" s="5">
@@ -10391,7 +10388,7 @@
     </row>
     <row r="54" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>24</v>
@@ -10400,7 +10397,7 @@
         <v>15</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="5">
@@ -10424,7 +10421,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>24</v>
@@ -10433,7 +10430,7 @@
         <v>12</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R54" s="2"/>
       <c r="S54" s="5">
@@ -10457,16 +10454,16 @@
     </row>
     <row r="55" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="5">
@@ -10490,7 +10487,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>24</v>
@@ -10499,7 +10496,7 @@
         <v>13</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R55" s="2"/>
       <c r="S55" s="5">
@@ -10523,16 +10520,16 @@
     </row>
     <row r="56" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="5">
@@ -10556,7 +10553,7 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>24</v>
@@ -10565,7 +10562,7 @@
         <v>14</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R56" s="2"/>
       <c r="S56" s="5">
@@ -10589,7 +10586,7 @@
     </row>
     <row r="57" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>24</v>
@@ -10598,7 +10595,7 @@
         <v>20</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="5">
@@ -10622,7 +10619,7 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>24</v>
@@ -10631,7 +10628,7 @@
         <v>15</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R57" s="2"/>
       <c r="S57" s="5">
@@ -10655,16 +10652,16 @@
     </row>
     <row r="58" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="5">
@@ -10688,7 +10685,7 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>24</v>
@@ -10697,7 +10694,7 @@
         <v>16</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R58" s="2"/>
       <c r="S58" s="5">
@@ -10721,16 +10718,16 @@
     </row>
     <row r="59" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="5">
@@ -10754,7 +10751,7 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
       <c r="N59" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>24</v>
@@ -10763,7 +10760,7 @@
         <v>17</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R59" s="2"/>
       <c r="S59" s="5">
@@ -10787,16 +10784,16 @@
     </row>
     <row r="60" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="5">
@@ -10820,7 +10817,7 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
       <c r="N60" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>24</v>
@@ -10829,7 +10826,7 @@
         <v>18</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R60" s="2"/>
       <c r="S60" s="5">
@@ -10853,16 +10850,16 @@
     </row>
     <row r="61" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="5">
@@ -10886,7 +10883,7 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
       <c r="N61" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>24</v>
@@ -10895,7 +10892,7 @@
         <v>19</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R61" s="2"/>
       <c r="S61" s="5">
@@ -10919,16 +10916,16 @@
     </row>
     <row r="62" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="5">
@@ -10952,7 +10949,7 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>24</v>
@@ -10961,7 +10958,7 @@
         <v>20</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R62" s="2"/>
       <c r="S62" s="5">
@@ -10985,16 +10982,16 @@
     </row>
     <row r="63" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="5">
@@ -11018,7 +11015,7 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>24</v>
@@ -11027,7 +11024,7 @@
         <v>21</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R63" s="2"/>
       <c r="S63" s="5">
@@ -11051,16 +11048,16 @@
     </row>
     <row r="64" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="5">
@@ -11084,7 +11081,7 @@
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>24</v>
@@ -11093,7 +11090,7 @@
         <v>22</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R64" s="2"/>
       <c r="S64" s="5">
@@ -11117,16 +11114,16 @@
     </row>
     <row r="65" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="5">
@@ -11150,7 +11147,7 @@
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>24</v>
@@ -11159,7 +11156,7 @@
         <v>23</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R65" s="2"/>
       <c r="S65" s="5">
@@ -11183,16 +11180,16 @@
     </row>
     <row r="66" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="5">
@@ -11216,7 +11213,7 @@
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>24</v>
@@ -11225,7 +11222,7 @@
         <v>24</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R66" s="2"/>
       <c r="S66" s="5">
@@ -11249,16 +11246,16 @@
     </row>
     <row r="67" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="5">
@@ -11282,7 +11279,7 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>24</v>
@@ -11291,7 +11288,7 @@
         <v>25</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R67" s="2"/>
       <c r="S67" s="5">
@@ -11315,16 +11312,16 @@
     </row>
     <row r="68" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="5">
@@ -11348,7 +11345,7 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>24</v>
@@ -11357,7 +11354,7 @@
         <v>26</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R68" s="2"/>
       <c r="S68" s="5">
@@ -11381,16 +11378,16 @@
     </row>
     <row r="69" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" s="5">
@@ -11414,7 +11411,7 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>24</v>
@@ -11423,7 +11420,7 @@
         <v>27</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R69" s="2"/>
       <c r="S69" s="5">
@@ -11447,16 +11444,16 @@
     </row>
     <row r="70" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" s="5">
@@ -11480,7 +11477,7 @@
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>24</v>
@@ -11489,7 +11486,7 @@
         <v>28</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R70" s="2"/>
       <c r="S70" s="5">
@@ -11513,16 +11510,16 @@
     </row>
     <row r="71" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="5">
@@ -11546,7 +11543,7 @@
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>24</v>
@@ -11555,7 +11552,7 @@
         <v>29</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R71" s="2"/>
       <c r="S71" s="5">
@@ -11579,16 +11576,16 @@
     </row>
     <row r="72" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="5">
@@ -11612,7 +11609,7 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>24</v>
@@ -11621,7 +11618,7 @@
         <v>30</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R72" s="2"/>
       <c r="S72" s="5">
@@ -11645,16 +11642,16 @@
     </row>
     <row r="73" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" s="5">
@@ -11678,7 +11675,7 @@
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>24</v>
@@ -11687,7 +11684,7 @@
         <v>31</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R73" s="2"/>
       <c r="S73" s="5">
@@ -11711,16 +11708,16 @@
     </row>
     <row r="74" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C74" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" s="5">
@@ -11744,7 +11741,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>24</v>
@@ -11753,7 +11750,7 @@
         <v>32</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R74" s="2"/>
       <c r="S74" s="5">
@@ -11777,7 +11774,7 @@
     </row>
     <row r="75" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>24</v>
@@ -11786,7 +11783,7 @@
         <v>18</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" s="5">
@@ -11810,7 +11807,7 @@
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>24</v>
@@ -11819,7 +11816,7 @@
         <v>33</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R75" s="2"/>
       <c r="S75" s="5">
@@ -11843,16 +11840,16 @@
     </row>
     <row r="76" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C76" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" s="5">
@@ -11876,7 +11873,7 @@
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>24</v>
@@ -11885,7 +11882,7 @@
         <v>34</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R76" s="2"/>
       <c r="S76" s="5">
@@ -11909,16 +11906,16 @@
     </row>
     <row r="77" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="5">
@@ -11942,7 +11939,7 @@
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>24</v>
@@ -11951,7 +11948,7 @@
         <v>35</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R77" s="2"/>
       <c r="S77" s="5">
@@ -11975,7 +11972,7 @@
     </row>
     <row r="78" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>24</v>
@@ -11984,7 +11981,7 @@
         <v>22</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" s="5">
@@ -12008,7 +12005,7 @@
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>24</v>
@@ -12017,7 +12014,7 @@
         <v>36</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R78" s="2"/>
       <c r="S78" s="5">
@@ -12041,16 +12038,16 @@
     </row>
     <row r="79" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C79" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" s="5">
@@ -12074,7 +12071,7 @@
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>24</v>
@@ -12083,7 +12080,7 @@
         <v>37</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R79" s="2"/>
       <c r="S79" s="5">
@@ -12107,16 +12104,16 @@
     </row>
     <row r="80" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C80" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" s="5">
@@ -12140,7 +12137,7 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>24</v>
@@ -12149,7 +12146,7 @@
         <v>38</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R80" s="2"/>
       <c r="S80" s="5">
@@ -12173,16 +12170,16 @@
     </row>
     <row r="81" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C81" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" s="5">
@@ -12206,7 +12203,7 @@
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>24</v>
@@ -12215,7 +12212,7 @@
         <v>39</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R81" s="2"/>
       <c r="S81" s="5">
@@ -12239,16 +12236,16 @@
     </row>
     <row r="82" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="5">
@@ -12272,7 +12269,7 @@
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>24</v>
@@ -12281,7 +12278,7 @@
         <v>40</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R82" s="2"/>
       <c r="S82" s="5">
@@ -12305,16 +12302,16 @@
     </row>
     <row r="83" spans="1:24" ht="32" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
@@ -12326,16 +12323,16 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R83" s="2"/>
       <c r="S83" s="5">
@@ -12359,16 +12356,16 @@
     </row>
     <row r="84" spans="1:24" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
@@ -12380,16 +12377,16 @@
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R84" s="2"/>
       <c r="S84" s="5">
@@ -12413,16 +12410,16 @@
     </row>
     <row r="85" spans="1:24" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
@@ -12434,16 +12431,16 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R85" s="2"/>
       <c r="S85" s="5">
@@ -12467,16 +12464,16 @@
     </row>
     <row r="86" spans="1:24" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
@@ -12488,16 +12485,16 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R86" s="2"/>
       <c r="S86" s="5">
@@ -12520,7 +12517,7 @@
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C87" s="17"/>
+      <c r="C87" s="12"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:K42">

--- a/results/mvp_primary_db.xlsx
+++ b/results/mvp_primary_db.xlsx
@@ -14777,34 +14777,36 @@
           <t>Attentive</t>
         </is>
       </c>
-      <c r="P83" s="14" t="inlineStr">
-        <is>
-          <t>noise_0.6_block_24</t>
-        </is>
+      <c r="P83" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="Q83" s="14" t="inlineStr">
         <is>
-          <t>noise_0.6_block_24</t>
-        </is>
-      </c>
-      <c r="R83" s="14" t="n"/>
+          <t>noise_0.8_block_24</t>
+        </is>
+      </c>
+      <c r="R83" s="14" t="inlineStr">
+        <is>
+          <t>1e-5</t>
+        </is>
+      </c>
       <c r="S83" s="5" t="n">
-        <v>96.6273187183811</v>
+        <v>90.33726812816188</v>
       </c>
       <c r="T83" s="5" t="n">
-        <v>91.50657229524769</v>
+        <v>83.67037411526795</v>
       </c>
       <c r="U83" s="5" t="n">
-        <v>89.4337714863498</v>
+        <v>81.85035389282103</v>
       </c>
       <c r="V83" s="5" t="n">
-        <v>93.4232715008431</v>
+        <v>81.75379426644183</v>
       </c>
       <c r="W83" s="5" t="n">
-        <v>84.7320525783619</v>
+        <v>69.66632962588474</v>
       </c>
       <c r="X83" s="5" t="n">
-        <v>80.5864509605662</v>
+        <v>66.83518705763397</v>
       </c>
     </row>
     <row r="84" ht="32" customHeight="1">
@@ -14863,34 +14865,36 @@
           <t>Attentive</t>
         </is>
       </c>
-      <c r="P84" s="14" t="inlineStr">
-        <is>
-          <t>noise_0.5_block_24</t>
-        </is>
+      <c r="P84" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="Q84" s="14" t="inlineStr">
         <is>
-          <t>noise_0.5_block_24</t>
-        </is>
-      </c>
-      <c r="R84" s="14" t="n"/>
+          <t>noise_0.6_block_24</t>
+        </is>
+      </c>
+      <c r="R84" s="14" t="inlineStr">
+        <is>
+          <t>1e-5</t>
+        </is>
+      </c>
       <c r="S84" s="5" t="n">
-        <v>98.3642495784148</v>
+        <v>94.56998313659359</v>
       </c>
       <c r="T84" s="5" t="n">
-        <v>91.6582406471183</v>
+        <v>87.86653185035389</v>
       </c>
       <c r="U84" s="5" t="n">
-        <v>91.7593528816986</v>
+        <v>86.65318503538928</v>
       </c>
       <c r="V84" s="5" t="n">
-        <v>96.7284991568296</v>
+        <v>89.78077571669478</v>
       </c>
       <c r="W84" s="5" t="n">
-        <v>84.5298281092012</v>
+        <v>78.36198179979777</v>
       </c>
       <c r="X84" s="5" t="n">
-        <v>84.32760364004039</v>
+        <v>75.32861476238625</v>
       </c>
     </row>
     <row r="85" ht="32" customHeight="1">
@@ -14949,34 +14953,36 @@
           <t>Attentive</t>
         </is>
       </c>
-      <c r="P85" s="14" t="inlineStr">
-        <is>
-          <t>noise_0.2_block_24</t>
-        </is>
+      <c r="P85" s="14" t="n">
+        <v>22</v>
       </c>
       <c r="Q85" s="14" t="inlineStr">
         <is>
-          <t>noise_0.2_block_24</t>
-        </is>
-      </c>
-      <c r="R85" s="14" t="n"/>
+          <t>noise_0.5_block_24</t>
+        </is>
+      </c>
+      <c r="R85" s="14" t="inlineStr">
+        <is>
+          <t>1e-5</t>
+        </is>
+      </c>
       <c r="S85" s="5" t="n">
-        <v>98.1281618887015</v>
+        <v>98.19561551433389</v>
       </c>
       <c r="T85" s="5" t="n">
-        <v>93.1243680485338</v>
+        <v>90.69767441860465</v>
       </c>
       <c r="U85" s="5" t="n">
-        <v>90.74823053589481</v>
+        <v>90.4448938321537</v>
       </c>
       <c r="V85" s="5" t="n">
-        <v>96.256323777403</v>
+        <v>96.39123102866779</v>
       </c>
       <c r="W85" s="5" t="n">
-        <v>86.95652173913039</v>
+        <v>83.41759352881699</v>
       </c>
       <c r="X85" s="5" t="n">
-        <v>83.0131445904954</v>
+        <v>82.30535894843275</v>
       </c>
     </row>
     <row r="86" ht="32" customHeight="1">
@@ -15035,34 +15041,36 @@
           <t>Attentive</t>
         </is>
       </c>
-      <c r="P86" s="14" t="inlineStr">
-        <is>
-          <t>noise_0.1_block_24</t>
-        </is>
+      <c r="P86" s="14" t="n">
+        <v>26</v>
       </c>
       <c r="Q86" s="14" t="inlineStr">
         <is>
-          <t>noise_0.1_block_24</t>
-        </is>
-      </c>
-      <c r="R86" s="14" t="n"/>
+          <t>noise_0.4_block_24</t>
+        </is>
+      </c>
+      <c r="R86" s="14" t="inlineStr">
+        <is>
+          <t>1e-5</t>
+        </is>
+      </c>
       <c r="S86" s="5" t="n">
-        <v>98.4485666104553</v>
+        <v>97.92580101180438</v>
       </c>
       <c r="T86" s="5" t="n">
-        <v>91.3549039433771</v>
+        <v>92.77047522750253</v>
       </c>
       <c r="U86" s="5" t="n">
-        <v>89.5854398382204</v>
+        <v>91.25379170879675</v>
       </c>
       <c r="V86" s="5" t="n">
-        <v>96.8971332209106</v>
+        <v>95.91905564924114</v>
       </c>
       <c r="W86" s="5" t="n">
-        <v>83.9231547017189</v>
+        <v>86.45096056622852</v>
       </c>
       <c r="X86" s="5" t="n">
-        <v>81.59757330636999</v>
+        <v>84.22649140546005</v>
       </c>
     </row>
     <row r="87">
